--- a/public/PDF/Microsoft Excel/ExcelExcercise/លំហាត់អនុវត្ត Excel page Setup 1.xlsx
+++ b/public/PDF/Microsoft Excel/ExcelExcercise/លំហាត់អនុវត្ត Excel page Setup 1.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Veasna\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Veasna\Desktop\SchoolApp\School-Web-Vite\public\PDF\Microsoft Excel\ExcelExcercise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8E591A5-E2E8-4F8E-81D7-F4FAB8DF96B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D955EF1-21A5-45B7-93C0-002E0A231A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F251868F-B9BA-41B7-932E-1AA6ACCC39AF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F251868F-B9BA-41B7-932E-1AA6ACCC39AF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ExcerciseI" sheetId="1" r:id="rId1"/>
+    <sheet name="ExcerciseII" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="117">
   <si>
     <t>ល.រ</t>
   </si>
@@ -295,6 +296,99 @@
   </si>
   <si>
     <t>វិចប ព្រះនរោត្តមសីហមុនី</t>
+  </si>
+  <si>
+    <t>ទឹកសុទ្ធ</t>
+  </si>
+  <si>
+    <t>ស្រាបៀ</t>
+  </si>
+  <si>
+    <t>ស្ទីង</t>
+  </si>
+  <si>
+    <t>សាម៉ារ៉ៃ</t>
+  </si>
+  <si>
+    <t>កូកាកូឡា</t>
+  </si>
+  <si>
+    <t>គោជល់</t>
+  </si>
+  <si>
+    <t>ខារ៉ាបាវ</t>
+  </si>
+  <si>
+    <t>អូអ៊ីឈិ</t>
+  </si>
+  <si>
+    <t>ប៉ិបស៊ី</t>
+  </si>
+  <si>
+    <t>ស្ដេចតែ</t>
+  </si>
+  <si>
+    <t>ត្រីខ</t>
+  </si>
+  <si>
+    <t>ទឹកដោះគោ</t>
+  </si>
+  <si>
+    <t>នំធុង</t>
+  </si>
+  <si>
+    <t>ថង់ផ្លាស្ទិក</t>
+  </si>
+  <si>
+    <t>ឆៃពៅ</t>
+  </si>
+  <si>
+    <t>កាពិ</t>
+  </si>
+  <si>
+    <t>ធ្យូង</t>
+  </si>
+  <si>
+    <t>ទឹកត្រី</t>
+  </si>
+  <si>
+    <t>ទឹកស៊ីអ៊ីវ</t>
+  </si>
+  <si>
+    <t>ប្រេងឆា</t>
+  </si>
+  <si>
+    <t>ប្រេងខ្យង</t>
+  </si>
+  <si>
+    <t>ស្ករស</t>
+  </si>
+  <si>
+    <t>ប៊ីចេង</t>
+  </si>
+  <si>
+    <t>ម្សៅស៊ុប</t>
+  </si>
+  <si>
+    <t>ទឹកខ្មេះ</t>
+  </si>
+  <si>
+    <t>ស្ករគ្រាប់</t>
+  </si>
+  <si>
+    <t>សូកូឡា</t>
+  </si>
+  <si>
+    <t>ថ្នាំដុះធ្មេញ</t>
+  </si>
+  <si>
+    <t>ដែកកេះ</t>
+  </si>
+  <si>
+    <t>ធូប</t>
+  </si>
+  <si>
+    <t>ទៀន</t>
   </si>
 </sst>
 </file>
@@ -388,12 +482,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -410,6 +504,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3556,4 +3653,172 @@
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E62122-9DCD-4282-9A97-19FE3EC5F182}">
+  <dimension ref="C5:C35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C5" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C6" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C7" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C8" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C9" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C10" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C11" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C12" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C13" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C14" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C15" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C16" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C17" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C18" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C19" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C20" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C21" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C22" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C23" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C24" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C25" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C26" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C27" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C28" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C29" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C30" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C31" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C32" s="10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C33" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C34" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="C35" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>